--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1503,7 +1503,7 @@
     <t>API-specifikation (logisk modell)</t>
   </si>
   <si>
-    <t>2026-09-08T10:34:42+00:00</t>
+    <t>2026-09-08T11:28:32+00:00</t>
   </si>
   <si>
     <t>Logisk modell för entiteten API-specifikation i informationsunderlaget. REST-exponering i det administrativa API:et är inte del av detta utkast — se REQ-MDL-4.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1503,7 +1503,7 @@
     <t>API-specifikation (logisk modell)</t>
   </si>
   <si>
-    <t>2026-09-08T11:28:32+00:00</t>
+    <t>2026-09-08T11:37:33+00:00</t>
   </si>
   <si>
     <t>Logisk modell för entiteten API-specifikation i informationsunderlaget. REST-exponering i det administrativa API:et är inte del av detta utkast — se REQ-MDL-4.</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6213" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6510" uniqueCount="805">
   <si>
     <t>Property</t>
   </si>
@@ -1503,7 +1503,7 @@
     <t>API-specifikation (logisk modell)</t>
   </si>
   <si>
-    <t>2026-09-08T11:37:33+00:00</t>
+    <t>2026-09-08T12:25:30+00:00</t>
   </si>
   <si>
     <t>Logisk modell för entiteten API-specifikation i informationsunderlaget. REST-exponering i det administrativa API:et är inte del av detta utkast — se REQ-MDL-4.</t>
@@ -1823,10 +1823,73 @@
     <t>Endpoint.identifier</t>
   </si>
   <si>
+    <t>Ändpunktsidentifierare, inklusive EHM:s motsvarande id</t>
+  </si>
+  <si>
+    <t>Identifier for the organization that is used to identify the endpoint across multiple disparate systems.</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier:ehmEndpointId</t>
+  </si>
+  <si>
+    <t>ehmEndpointId</t>
+  </si>
+  <si>
     <t>Identifies this endpoint across multiple systems</t>
   </si>
   <si>
-    <t>Identifier for the organization that is used to identify the endpoint across multiple disparate systems.</t>
+    <t>Endpoint.identifier:ehmEndpointId.id</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier.id</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier:ehmEndpointId.extension</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier.extension</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier:ehmEndpointId.use</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier.use</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier:ehmEndpointId.type</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier.type</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier:ehmEndpointId.system</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier.system</t>
+  </si>
+  <si>
+    <t>http://electronichealth.se/fhir/NDI/Endpoint</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier:ehmEndpointId.value</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier.value</t>
+  </si>
+  <si>
+    <t>EHM:s logiska id (UUID) för samma ändpunkt i deras register</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier:ehmEndpointId.period</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier.period</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier:ehmEndpointId.assigner</t>
+  </si>
+  <si>
+    <t>Endpoint.identifier.assigner</t>
   </si>
   <si>
     <t>Endpoint.status</t>
@@ -2230,7 +2293,7 @@
     <t>Organization.identifier.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.752.29.4.13</t>
+    <t>urn:oid:2.5.4.97</t>
   </si>
   <si>
     <t>Organization.identifier:organisationsnummer.value</t>
@@ -3636,7 +3699,7 @@
         <v>2</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>654</v>
+        <v>675</v>
       </c>
     </row>
     <row r="134">
@@ -3644,7 +3707,7 @@
         <v>4</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>655</v>
+        <v>676</v>
       </c>
     </row>
     <row r="135">
@@ -3660,7 +3723,7 @@
         <v>9</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>656</v>
+        <v>677</v>
       </c>
     </row>
     <row r="137">
@@ -3668,7 +3731,7 @@
         <v>10</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>657</v>
+        <v>678</v>
       </c>
     </row>
     <row r="138">
@@ -3722,7 +3785,7 @@
         <v>23</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>658</v>
+        <v>679</v>
       </c>
     </row>
     <row r="145">
@@ -3758,7 +3821,7 @@
         <v>31</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>655</v>
+        <v>676</v>
       </c>
     </row>
     <row r="150">
@@ -3798,7 +3861,7 @@
         <v>2</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
     </row>
     <row r="155">
@@ -3806,7 +3869,7 @@
         <v>4</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>671</v>
+        <v>692</v>
       </c>
     </row>
     <row r="156">
@@ -3814,7 +3877,7 @@
         <v>6</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>672</v>
+        <v>693</v>
       </c>
     </row>
     <row r="157">
@@ -3830,7 +3893,7 @@
         <v>9</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>672</v>
+        <v>693</v>
       </c>
     </row>
     <row r="159">
@@ -3838,7 +3901,7 @@
         <v>10</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>673</v>
+        <v>694</v>
       </c>
     </row>
     <row r="160">
@@ -3892,7 +3955,7 @@
         <v>23</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>674</v>
+        <v>695</v>
       </c>
     </row>
     <row r="167">
@@ -3928,7 +3991,7 @@
         <v>31</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>675</v>
+        <v>696</v>
       </c>
     </row>
     <row r="172">
@@ -3936,7 +3999,7 @@
         <v>33</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>676</v>
+        <v>697</v>
       </c>
     </row>
     <row r="173">
@@ -3968,7 +4031,7 @@
         <v>2</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>777</v>
+        <v>798</v>
       </c>
     </row>
     <row r="177">
@@ -3976,7 +4039,7 @@
         <v>4</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>778</v>
+        <v>799</v>
       </c>
     </row>
     <row r="178">
@@ -3992,7 +4055,7 @@
         <v>9</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>779</v>
+        <v>800</v>
       </c>
     </row>
     <row r="180">
@@ -4000,7 +4063,7 @@
         <v>10</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>780</v>
+        <v>801</v>
       </c>
     </row>
     <row r="181">
@@ -4054,7 +4117,7 @@
         <v>23</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>781</v>
+        <v>802</v>
       </c>
     </row>
     <row r="188">
@@ -4090,7 +4153,7 @@
         <v>31</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>778</v>
+        <v>799</v>
       </c>
     </row>
     <row r="193">
@@ -4124,7 +4187,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK177"/>
+  <dimension ref="A1:AK186"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="29.12890625" customWidth="true" bestFit="true"/>
@@ -16130,7 +16193,7 @@
         <v>77</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J115" t="s" s="2">
         <v>78</v>
@@ -16184,16 +16247,14 @@
         <v>78</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="AD115" s="2"/>
       <c r="AE115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>575</v>
@@ -16219,15 +16280,17 @@
         <v>578</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="D116" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="D116" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="E116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>84</v>
@@ -16236,23 +16299,21 @@
         <v>85</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>581</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" s="2"/>
       <c r="Q116" t="s" s="2">
         <v>78</v>
@@ -16277,13 +16338,13 @@
         <v>78</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>582</v>
+        <v>78</v>
       </c>
       <c r="AA116" t="s" s="2">
-        <v>583</v>
+        <v>78</v>
       </c>
       <c r="AB116" t="s" s="2">
         <v>78</v>
@@ -16301,13 +16362,13 @@
         <v>78</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>78</v>
@@ -16321,10 +16382,10 @@
         <v>551</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -16332,32 +16393,30 @@
       </c>
       <c r="F117" s="2"/>
       <c r="G117" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>585</v>
+        <v>153</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>587</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O117" s="2"/>
       <c r="P117" s="2"/>
       <c r="Q117" t="s" s="2">
         <v>78</v>
@@ -16382,11 +16441,13 @@
         <v>78</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="Z117" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AA117" t="s" s="2">
-        <v>588</v>
+        <v>78</v>
       </c>
       <c r="AB117" t="s" s="2">
         <v>78</v>
@@ -16404,19 +16465,19 @@
         <v>78</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>584</v>
+        <v>155</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="118">
@@ -16424,41 +16485,43 @@
         <v>551</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>590</v>
+        <v>131</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O118" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="P118" s="2"/>
       <c r="Q118" t="s" s="2">
         <v>78</v>
@@ -16495,31 +16558,31 @@
         <v>78</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="AD118" t="s" s="2">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="AE118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>589</v>
+        <v>162</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="119">
@@ -16527,10 +16590,10 @@
         <v>551</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -16547,22 +16610,26 @@
         <v>78</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>593</v>
+        <v>165</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O119" s="2"/>
-      <c r="P119" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="Q119" t="s" s="2">
         <v>78</v>
       </c>
@@ -16586,13 +16653,13 @@
         <v>78</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="AA119" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="AB119" t="s" s="2">
         <v>78</v>
@@ -16610,7 +16677,7 @@
         <v>78</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>592</v>
+        <v>171</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>76</v>
@@ -16630,10 +16697,10 @@
         <v>551</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -16644,7 +16711,7 @@
         <v>76</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>78</v>
@@ -16659,13 +16726,17 @@
         <v>174</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>596</v>
+        <v>175</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="O120" s="2"/>
-      <c r="P120" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="Q120" t="s" s="2">
         <v>78</v>
       </c>
@@ -16691,9 +16762,11 @@
       <c r="Y120" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Z120" s="2"/>
+      <c r="Z120" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="AA120" t="s" s="2">
-        <v>598</v>
+        <v>181</v>
       </c>
       <c r="AB120" t="s" s="2">
         <v>78</v>
@@ -16711,13 +16784,13 @@
         <v>78</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>595</v>
+        <v>182</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>78</v>
@@ -16731,10 +16804,10 @@
         <v>551</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -16748,7 +16821,7 @@
         <v>84</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J121" t="s" s="2">
         <v>78</v>
@@ -16757,18 +16830,20 @@
         <v>85</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>509</v>
+        <v>98</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>600</v>
+        <v>185</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>601</v>
+        <v>186</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="P121" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="Q121" t="s" s="2">
         <v>78</v>
       </c>
@@ -16777,10 +16852,10 @@
         <v>78</v>
       </c>
       <c r="T121" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="U121" t="s" s="2">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="V121" t="s" s="2">
         <v>78</v>
@@ -16816,7 +16891,7 @@
         <v>78</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>599</v>
+        <v>191</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>76</v>
@@ -16836,10 +16911,10 @@
         <v>551</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -16847,30 +16922,32 @@
       </c>
       <c r="F122" s="2"/>
       <c r="G122" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>269</v>
+        <v>194</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="O122" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P122" s="2"/>
       <c r="Q122" t="s" s="2">
         <v>78</v>
@@ -16883,7 +16960,7 @@
         <v>78</v>
       </c>
       <c r="U122" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="V122" t="s" s="2">
         <v>78</v>
@@ -16919,16 +16996,16 @@
         <v>78</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>603</v>
+        <v>199</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>96</v>
@@ -16939,10 +17016,10 @@
         <v>551</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -16956,7 +17033,7 @@
         <v>84</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J123" t="s" s="2">
         <v>78</v>
@@ -16968,14 +17045,12 @@
         <v>203</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>607</v>
+        <v>204</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>609</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" s="2"/>
       <c r="Q123" t="s" s="2">
         <v>78</v>
@@ -17024,7 +17099,7 @@
         <v>78</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>606</v>
+        <v>206</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>76</v>
@@ -17044,10 +17119,10 @@
         <v>551</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -17067,18 +17142,20 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>86</v>
+        <v>209</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>153</v>
+        <v>210</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O124" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P124" s="2"/>
       <c r="Q124" t="s" s="2">
         <v>78</v>
@@ -17127,7 +17204,7 @@
         <v>78</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>76</v>
@@ -17136,10 +17213,10 @@
         <v>84</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="125">
@@ -17147,42 +17224,42 @@
         <v>551</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>131</v>
+        <v>600</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>159</v>
+        <v>601</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>133</v>
+        <v>602</v>
       </c>
       <c r="P125" s="2"/>
       <c r="Q125" t="s" s="2">
@@ -17208,43 +17285,43 @@
         <v>78</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>78</v>
+        <v>603</v>
       </c>
       <c r="AA125" t="s" s="2">
-        <v>78</v>
+        <v>604</v>
       </c>
       <c r="AB125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="AD125" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="AE125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>162</v>
+        <v>599</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="126">
@@ -17252,10 +17329,10 @@
         <v>551</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -17263,10 +17340,10 @@
       </c>
       <c r="F126" s="2"/>
       <c r="G126" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>85</v>
@@ -17278,16 +17355,16 @@
         <v>85</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>613</v>
+        <v>174</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="P126" s="2"/>
       <c r="Q126" t="s" s="2">
@@ -17313,13 +17390,11 @@
         <v>78</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="Z126" s="2"/>
       <c r="AA126" t="s" s="2">
-        <v>78</v>
+        <v>609</v>
       </c>
       <c r="AB126" t="s" s="2">
         <v>78</v>
@@ -17337,16 +17412,16 @@
         <v>78</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>618</v>
+        <v>78</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>96</v>
@@ -17357,10 +17432,10 @@
         <v>551</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -17368,7 +17443,7 @@
       </c>
       <c r="F127" s="2"/>
       <c r="G127" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>84</v>
@@ -17383,24 +17458,20 @@
         <v>85</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>613</v>
+        <v>194</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>622</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="O127" s="2"/>
       <c r="P127" s="2"/>
       <c r="Q127" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="R127" t="s" s="2">
-        <v>623</v>
-      </c>
+      <c r="R127" s="2"/>
       <c r="S127" t="s" s="2">
         <v>78</v>
       </c>
@@ -17444,7 +17515,7 @@
         <v>78</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>76</v>
@@ -17453,7 +17524,7 @@
         <v>84</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>618</v>
+        <v>78</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>96</v>
@@ -17464,10 +17535,10 @@
         <v>551</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -17478,29 +17549,27 @@
         <v>76</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K128" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="J128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="L128" t="s" s="2">
-        <v>383</v>
+        <v>194</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>628</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" s="2"/>
       <c r="Q128" t="s" s="2">
         <v>78</v>
@@ -17549,13 +17618,13 @@
         <v>78</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>78</v>
@@ -17569,10 +17638,10 @@
         <v>551</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -17583,7 +17652,7 @@
         <v>76</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>78</v>
@@ -17592,16 +17661,16 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>153</v>
+        <v>617</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>154</v>
+        <v>618</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" s="2"/>
@@ -17628,13 +17697,11 @@
         <v>78</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Z129" s="2"/>
       <c r="AA129" t="s" s="2">
-        <v>78</v>
+        <v>619</v>
       </c>
       <c r="AB129" t="s" s="2">
         <v>78</v>
@@ -17652,19 +17719,19 @@
         <v>78</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>155</v>
+        <v>616</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="130">
@@ -17672,10 +17739,10 @@
         <v>551</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -17683,30 +17750,32 @@
       </c>
       <c r="F130" s="2"/>
       <c r="G130" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I130" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J130" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>130</v>
+        <v>509</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>521</v>
+        <v>621</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O130" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="P130" s="2"/>
       <c r="Q130" t="s" s="2">
         <v>78</v>
@@ -17743,29 +17812,31 @@
         <v>78</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AD130" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AE130" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>162</v>
+        <v>620</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="131">
@@ -17773,14 +17844,12 @@
         <v>551</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="D131" t="s" s="2">
-        <v>632</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
         <v>78</v>
       </c>
@@ -17792,7 +17861,7 @@
         <v>77</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J131" t="s" s="2">
         <v>78</v>
@@ -17801,13 +17870,13 @@
         <v>78</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>633</v>
+        <v>269</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>539</v>
+        <v>625</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>540</v>
+        <v>626</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
@@ -17858,7 +17927,7 @@
         <v>78</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>162</v>
+        <v>624</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>76</v>
@@ -17870,7 +17939,7 @@
         <v>78</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="132">
@@ -17878,46 +17947,44 @@
         <v>551</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
-        <v>392</v>
+        <v>78</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K132" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>393</v>
+        <v>628</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>394</v>
+        <v>629</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="P132" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="P132" s="2"/>
       <c r="Q132" t="s" s="2">
         <v>78</v>
       </c>
@@ -17965,19 +18032,19 @@
         <v>78</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>395</v>
+        <v>627</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="133">
@@ -17985,10 +18052,10 @@
         <v>551</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -17996,32 +18063,30 @@
       </c>
       <c r="F133" s="2"/>
       <c r="G133" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J133" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>636</v>
+        <v>153</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O133" s="2"/>
       <c r="P133" s="2"/>
       <c r="Q133" t="s" s="2">
         <v>78</v>
@@ -18046,11 +18111,13 @@
         <v>78</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="Z133" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AA133" t="s" s="2">
-        <v>639</v>
+        <v>78</v>
       </c>
       <c r="AB133" t="s" s="2">
         <v>78</v>
@@ -18068,19 +18135,19 @@
         <v>78</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>635</v>
+        <v>155</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="134">
@@ -18088,14 +18155,14 @@
         <v>551</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="F134" s="2"/>
       <c r="G134" t="s" s="2">
@@ -18111,19 +18178,19 @@
         <v>78</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>641</v>
+        <v>131</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>642</v>
+        <v>159</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>643</v>
+        <v>133</v>
       </c>
       <c r="P134" s="2"/>
       <c r="Q134" t="s" s="2">
@@ -18149,31 +18216,31 @@
         <v>78</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>644</v>
+        <v>78</v>
       </c>
       <c r="AA134" t="s" s="2">
-        <v>645</v>
+        <v>78</v>
       </c>
       <c r="AB134" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="AD134" t="s" s="2">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="AE134" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>640</v>
+        <v>162</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>76</v>
@@ -18185,7 +18252,7 @@
         <v>78</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="135">
@@ -18193,10 +18260,10 @@
         <v>551</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -18204,7 +18271,7 @@
       </c>
       <c r="F135" s="2"/>
       <c r="G135" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>84</v>
@@ -18219,16 +18286,16 @@
         <v>85</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>495</v>
+        <v>634</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="P135" s="2"/>
       <c r="Q135" t="s" s="2">
@@ -18278,16 +18345,16 @@
         <v>78</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>78</v>
+        <v>639</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>96</v>
@@ -18298,10 +18365,10 @@
         <v>551</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -18312,34 +18379,36 @@
         <v>76</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I136" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J136" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>194</v>
+        <v>634</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="P136" s="2"/>
       <c r="Q136" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="R136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>644</v>
+      </c>
       <c r="S136" t="s" s="2">
         <v>78</v>
       </c>
@@ -18383,16 +18452,16 @@
         <v>78</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>78</v>
+        <v>639</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>96</v>
@@ -18400,13 +18469,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>654</v>
+        <v>551</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -18420,7 +18489,7 @@
         <v>77</v>
       </c>
       <c r="I137" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J137" t="s" s="2">
         <v>78</v>
@@ -18429,15 +18498,17 @@
         <v>78</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="O137" s="2"/>
+        <v>648</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>649</v>
+      </c>
       <c r="P137" s="2"/>
       <c r="Q137" t="s" s="2">
         <v>78</v>
@@ -18486,7 +18557,7 @@
         <v>78</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>480</v>
+        <v>646</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>76</v>
@@ -18498,18 +18569,18 @@
         <v>78</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>654</v>
+        <v>551</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -18517,7 +18588,7 @@
       </c>
       <c r="F138" s="2"/>
       <c r="G138" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>84</v>
@@ -18532,13 +18603,13 @@
         <v>78</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>86</v>
+        <v>194</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>660</v>
+        <v>153</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>661</v>
+        <v>154</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" s="2"/>
@@ -18589,16 +18660,16 @@
         <v>78</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>659</v>
+        <v>155</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>78</v>
@@ -18606,13 +18677,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>654</v>
+        <v>551</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -18620,10 +18691,10 @@
       </c>
       <c r="F139" s="2"/>
       <c r="G139" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>78</v>
@@ -18635,13 +18706,13 @@
         <v>78</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>663</v>
+        <v>130</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>664</v>
+        <v>521</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>665</v>
+        <v>527</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" s="2"/>
@@ -18680,56 +18751,56 @@
         <v>78</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AD139" s="2"/>
       <c r="AE139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>662</v>
+        <v>162</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>654</v>
+        <v>551</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="D140" s="2"/>
+        <v>651</v>
+      </c>
+      <c r="D140" t="s" s="2">
+        <v>653</v>
+      </c>
       <c r="E140" t="s" s="2">
         <v>78</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J140" t="s" s="2">
         <v>78</v>
@@ -18738,13 +18809,13 @@
         <v>78</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>668</v>
+        <v>539</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>669</v>
+        <v>540</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
@@ -18795,34 +18866,34 @@
         <v>78</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>666</v>
+        <v>162</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>670</v>
+        <v>551</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>675</v>
+        <v>655</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>675</v>
+        <v>655</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" t="s" s="2">
@@ -18835,22 +18906,26 @@
         <v>78</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>677</v>
+        <v>393</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="O141" s="2"/>
-      <c r="P141" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="P141" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="Q141" t="s" s="2">
         <v>78</v>
       </c>
@@ -18898,7 +18973,7 @@
         <v>78</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>675</v>
+        <v>395</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>76</v>
@@ -18910,18 +18985,18 @@
         <v>78</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>679</v>
+        <v>135</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>670</v>
+        <v>551</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>680</v>
+        <v>656</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>680</v>
+        <v>656</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -18929,7 +19004,7 @@
       </c>
       <c r="F142" s="2"/>
       <c r="G142" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>84</v>
@@ -18944,16 +19019,16 @@
         <v>85</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>87</v>
+        <v>657</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>88</v>
+        <v>658</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>89</v>
+        <v>659</v>
       </c>
       <c r="P142" s="2"/>
       <c r="Q142" t="s" s="2">
@@ -18979,13 +19054,11 @@
         <v>78</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="Z142" s="2"/>
       <c r="AA142" t="s" s="2">
-        <v>78</v>
+        <v>660</v>
       </c>
       <c r="AB142" t="s" s="2">
         <v>78</v>
@@ -19003,30 +19076,30 @@
         <v>78</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>90</v>
+        <v>656</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>670</v>
+        <v>551</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>681</v>
+        <v>661</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>681</v>
+        <v>661</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -19037,7 +19110,7 @@
         <v>76</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>78</v>
@@ -19049,15 +19122,17 @@
         <v>85</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>93</v>
+        <v>662</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O143" s="2"/>
+        <v>663</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>664</v>
+      </c>
       <c r="P143" s="2"/>
       <c r="Q143" t="s" s="2">
         <v>78</v>
@@ -19082,13 +19157,13 @@
         <v>78</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>78</v>
+        <v>665</v>
       </c>
       <c r="AA143" t="s" s="2">
-        <v>78</v>
+        <v>666</v>
       </c>
       <c r="AB143" t="s" s="2">
         <v>78</v>
@@ -19106,13 +19181,13 @@
         <v>78</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>95</v>
+        <v>661</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>78</v>
@@ -19123,13 +19198,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>670</v>
+        <v>551</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>682</v>
+        <v>667</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>682</v>
+        <v>667</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -19137,31 +19212,31 @@
       </c>
       <c r="F144" s="2"/>
       <c r="G144" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I144" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K144" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>98</v>
+        <v>495</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>99</v>
+        <v>668</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>100</v>
+        <v>669</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>101</v>
+        <v>670</v>
       </c>
       <c r="P144" s="2"/>
       <c r="Q144" t="s" s="2">
@@ -19211,10 +19286,10 @@
         <v>78</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>102</v>
+        <v>667</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>84</v>
@@ -19228,13 +19303,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>670</v>
+        <v>551</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -19245,7 +19320,7 @@
         <v>76</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>78</v>
@@ -19257,16 +19332,16 @@
         <v>78</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>105</v>
+        <v>672</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>106</v>
+        <v>673</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>107</v>
+        <v>674</v>
       </c>
       <c r="P145" s="2"/>
       <c r="Q145" t="s" s="2">
@@ -19292,13 +19367,13 @@
         <v>78</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AA145" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AB145" t="s" s="2">
         <v>78</v>
@@ -19316,13 +19391,13 @@
         <v>78</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>111</v>
+        <v>671</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>78</v>
@@ -19333,24 +19408,24 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>78</v>
@@ -19362,17 +19437,15 @@
         <v>78</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>115</v>
+        <v>678</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>679</v>
+      </c>
+      <c r="O146" s="2"/>
       <c r="P146" s="2"/>
       <c r="Q146" t="s" s="2">
         <v>78</v>
@@ -19421,41 +19494,41 @@
         <v>78</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>118</v>
+        <v>480</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="F147" s="2"/>
       <c r="G147" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>78</v>
@@ -19467,17 +19540,15 @@
         <v>78</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>123</v>
+        <v>681</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>125</v>
-      </c>
+        <v>682</v>
+      </c>
+      <c r="O147" s="2"/>
       <c r="P147" s="2"/>
       <c r="Q147" t="s" s="2">
         <v>78</v>
@@ -19526,16 +19597,16 @@
         <v>78</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>126</v>
+        <v>680</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>78</v>
@@ -19543,24 +19614,24 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="F148" s="2"/>
       <c r="G148" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>78</v>
@@ -19572,17 +19643,15 @@
         <v>78</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>130</v>
+        <v>684</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>131</v>
+        <v>685</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>686</v>
+      </c>
+      <c r="O148" s="2"/>
       <c r="P148" s="2"/>
       <c r="Q148" t="s" s="2">
         <v>78</v>
@@ -19631,24 +19700,24 @@
         <v>78</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>134</v>
+        <v>683</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>687</v>
@@ -19658,39 +19727,35 @@
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="F149" s="2"/>
       <c r="G149" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>130</v>
+        <v>688</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>137</v>
+        <v>689</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="P149" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>690</v>
+      </c>
+      <c r="O149" s="2"/>
+      <c r="P149" s="2"/>
       <c r="Q149" t="s" s="2">
         <v>78</v>
       </c>
@@ -19738,30 +19803,30 @@
         <v>78</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>140</v>
+        <v>687</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -19775,27 +19840,25 @@
         <v>77</v>
       </c>
       <c r="I150" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J150" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="O150" s="2"/>
-      <c r="P150" t="s" s="2">
-        <v>691</v>
-      </c>
+      <c r="P150" s="2"/>
       <c r="Q150" t="s" s="2">
         <v>78</v>
       </c>
@@ -19831,17 +19894,19 @@
         <v>78</v>
       </c>
       <c r="AC150" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AD150" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AE150" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>76</v>
@@ -19850,25 +19915,23 @@
         <v>77</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>692</v>
+        <v>78</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>96</v>
+        <v>700</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="D151" t="s" s="2">
-        <v>694</v>
-      </c>
+        <v>701</v>
+      </c>
+      <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
         <v>78</v>
       </c>
@@ -19889,18 +19952,18 @@
         <v>85</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>695</v>
+        <v>87</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="O151" s="2"/>
-      <c r="P151" t="s" s="2">
-        <v>691</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="P151" s="2"/>
       <c r="Q151" t="s" s="2">
         <v>78</v>
       </c>
@@ -19948,30 +20011,30 @@
         <v>78</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>688</v>
+        <v>90</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>692</v>
+        <v>78</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -19991,16 +20054,16 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
@@ -20051,7 +20114,7 @@
         <v>78</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>76</v>
@@ -20060,53 +20123,53 @@
         <v>84</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="F153" s="2"/>
       <c r="G153" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="P153" s="2"/>
       <c r="Q153" t="s" s="2">
@@ -20144,42 +20207,42 @@
         <v>78</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="AD153" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="AE153" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ153" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -20196,26 +20259,24 @@
         <v>78</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L154" t="s" s="2">
         <v>104</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="P154" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="P154" s="2"/>
       <c r="Q154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20242,10 +20303,10 @@
         <v>108</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="AA154" t="s" s="2">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AB154" t="s" s="2">
         <v>78</v>
@@ -20263,7 +20324,7 @@
         <v>78</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>76</v>
@@ -20280,17 +20341,17 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F155" s="2"/>
       <c r="G155" t="s" s="2">
@@ -20306,23 +20367,21 @@
         <v>78</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="P155" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="P155" s="2"/>
       <c r="Q155" t="s" s="2">
         <v>78</v>
       </c>
@@ -20346,13 +20405,13 @@
         <v>78</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="AA155" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="AB155" t="s" s="2">
         <v>78</v>
@@ -20370,7 +20429,7 @@
         <v>78</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>76</v>
@@ -20379,7 +20438,7 @@
         <v>84</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>96</v>
@@ -20387,24 +20446,24 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="F156" s="2"/>
       <c r="G156" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>78</v>
@@ -20413,23 +20472,21 @@
         <v>78</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>185</v>
+        <v>123</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="P156" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="P156" s="2"/>
       <c r="Q156" t="s" s="2">
         <v>78</v>
       </c>
@@ -20438,10 +20495,10 @@
         <v>78</v>
       </c>
       <c r="T156" t="s" s="2">
-        <v>706</v>
+        <v>78</v>
       </c>
       <c r="U156" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="V156" t="s" s="2">
         <v>78</v>
@@ -20477,62 +20534,62 @@
         <v>78</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>191</v>
+        <v>126</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>707</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="F157" s="2"/>
       <c r="G157" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I157" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>709</v>
+        <v>131</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>196</v>
+        <v>132</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="P157" s="2"/>
       <c r="Q157" t="s" s="2">
@@ -20546,7 +20603,7 @@
         <v>78</v>
       </c>
       <c r="U157" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="V157" t="s" s="2">
         <v>78</v>
@@ -20582,62 +20639,66 @@
         <v>78</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>199</v>
+        <v>134</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="F158" s="2"/>
       <c r="G158" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K158" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>203</v>
+        <v>130</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>204</v>
+        <v>137</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O158" s="2"/>
-      <c r="P158" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="P158" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="Q158" t="s" s="2">
         <v>78</v>
       </c>
@@ -20685,30 +20746,30 @@
         <v>78</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>206</v>
+        <v>140</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -20719,10 +20780,10 @@
         <v>76</v>
       </c>
       <c r="H159" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I159" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J159" t="s" s="2">
         <v>78</v>
@@ -20731,18 +20792,18 @@
         <v>85</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>209</v>
+        <v>142</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>210</v>
+        <v>710</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="P159" s="2"/>
+        <v>711</v>
+      </c>
+      <c r="O159" s="2"/>
+      <c r="P159" t="s" s="2">
+        <v>712</v>
+      </c>
       <c r="Q159" t="s" s="2">
         <v>78</v>
       </c>
@@ -20778,28 +20839,26 @@
         <v>78</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD159" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="AD159" s="2"/>
       <c r="AE159" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>213</v>
+        <v>709</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>78</v>
+        <v>713</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>96</v>
@@ -20807,15 +20866,17 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>714</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="D160" s="2"/>
+        <v>709</v>
+      </c>
+      <c r="D160" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="E160" t="s" s="2">
         <v>78</v>
       </c>
@@ -20827,35 +20888,31 @@
         <v>84</v>
       </c>
       <c r="I160" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K160" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>215</v>
+        <v>142</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>717</v>
-      </c>
+        <v>711</v>
+      </c>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="Q160" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="R160" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="R160" s="2"/>
       <c r="S160" t="s" s="2">
         <v>78</v>
       </c>
@@ -20899,16 +20956,16 @@
         <v>78</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>78</v>
+        <v>713</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>96</v>
@@ -20916,13 +20973,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -20933,7 +20990,7 @@
         <v>76</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>78</v>
@@ -20942,23 +20999,19 @@
         <v>78</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>720</v>
+        <v>153</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="P161" t="s" s="2">
-        <v>723</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O161" s="2"/>
+      <c r="P161" s="2"/>
       <c r="Q161" t="s" s="2">
         <v>78</v>
       </c>
@@ -20982,13 +21035,13 @@
         <v>78</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>549</v>
+        <v>78</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>724</v>
+        <v>78</v>
       </c>
       <c r="AA161" t="s" s="2">
-        <v>725</v>
+        <v>78</v>
       </c>
       <c r="AB161" t="s" s="2">
         <v>78</v>
@@ -21006,66 +21059,64 @@
         <v>78</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>719</v>
+        <v>155</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="F162" s="2"/>
       <c r="G162" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I162" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J162" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>727</v>
+        <v>131</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>728</v>
+        <v>159</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="P162" t="s" s="2">
-        <v>730</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="P162" s="2"/>
       <c r="Q162" t="s" s="2">
         <v>78</v>
       </c>
@@ -21101,42 +21152,42 @@
         <v>78</v>
       </c>
       <c r="AC162" t="s" s="2">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="AD162" t="s" s="2">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="AE162" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>726</v>
+        <v>162</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>692</v>
+        <v>78</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -21147,31 +21198,31 @@
         <v>76</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>732</v>
+        <v>165</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>733</v>
+        <v>166</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>734</v>
+        <v>167</v>
       </c>
       <c r="P163" t="s" s="2">
-        <v>735</v>
+        <v>168</v>
       </c>
       <c r="Q163" t="s" s="2">
         <v>78</v>
@@ -21196,13 +21247,13 @@
         <v>78</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="AA163" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="AB163" t="s" s="2">
         <v>78</v>
@@ -21220,13 +21271,13 @@
         <v>78</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>731</v>
+        <v>171</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>78</v>
@@ -21237,13 +21288,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -21266,17 +21317,19 @@
         <v>85</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>505</v>
+        <v>174</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>737</v>
+        <v>175</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P164" t="s" s="2">
-        <v>739</v>
+        <v>178</v>
       </c>
       <c r="Q164" t="s" s="2">
         <v>78</v>
@@ -21301,13 +21354,13 @@
         <v>78</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="AA164" t="s" s="2">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="AB164" t="s" s="2">
         <v>78</v>
@@ -21325,7 +21378,7 @@
         <v>78</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>736</v>
+        <v>182</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>76</v>
@@ -21342,13 +21395,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>740</v>
+        <v>725</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>740</v>
+        <v>726</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -21356,10 +21409,10 @@
       </c>
       <c r="F165" s="2"/>
       <c r="G165" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>78</v>
@@ -21368,22 +21421,22 @@
         <v>78</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>741</v>
+        <v>98</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>742</v>
+        <v>185</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>743</v>
+        <v>186</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>744</v>
+        <v>187</v>
       </c>
       <c r="P165" t="s" s="2">
-        <v>745</v>
+        <v>188</v>
       </c>
       <c r="Q165" t="s" s="2">
         <v>78</v>
@@ -21393,10 +21446,10 @@
         <v>78</v>
       </c>
       <c r="T165" t="s" s="2">
-        <v>78</v>
+        <v>727</v>
       </c>
       <c r="U165" t="s" s="2">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="V165" t="s" s="2">
         <v>78</v>
@@ -21432,30 +21485,30 @@
         <v>78</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>740</v>
+        <v>191</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>746</v>
+        <v>96</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>747</v>
+        <v>729</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -21463,13 +21516,13 @@
       </c>
       <c r="F166" s="2"/>
       <c r="G166" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I166" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J166" t="s" s="2">
         <v>78</v>
@@ -21478,18 +21531,18 @@
         <v>85</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="O166" s="2"/>
-      <c r="P166" t="s" s="2">
-        <v>750</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="O166" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="P166" s="2"/>
       <c r="Q166" t="s" s="2">
         <v>78</v>
       </c>
@@ -21501,7 +21554,7 @@
         <v>78</v>
       </c>
       <c r="U166" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="V166" t="s" s="2">
         <v>78</v>
@@ -21537,7 +21590,7 @@
         <v>78</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>747</v>
+        <v>199</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>76</v>
@@ -21546,7 +21599,7 @@
         <v>84</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>96</v>
@@ -21554,13 +21607,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>751</v>
+        <v>731</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -21571,30 +21624,28 @@
         <v>76</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K167" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="J167" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K167" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="L167" t="s" s="2">
-        <v>752</v>
+        <v>203</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>753</v>
+        <v>204</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>754</v>
+        <v>205</v>
       </c>
       <c r="O167" s="2"/>
-      <c r="P167" t="s" s="2">
-        <v>755</v>
-      </c>
+      <c r="P167" s="2"/>
       <c r="Q167" t="s" s="2">
         <v>78</v>
       </c>
@@ -21642,13 +21693,13 @@
         <v>78</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>751</v>
+        <v>206</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>78</v>
@@ -21659,13 +21710,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>756</v>
+        <v>733</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>756</v>
+        <v>734</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -21676,7 +21727,7 @@
         <v>76</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>78</v>
@@ -21685,18 +21736,20 @@
         <v>78</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>383</v>
+        <v>209</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>757</v>
+        <v>210</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="O168" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="O168" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P168" s="2"/>
       <c r="Q168" t="s" s="2">
         <v>78</v>
@@ -21745,13 +21798,13 @@
         <v>78</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>756</v>
+        <v>213</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>78</v>
@@ -21762,13 +21815,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>759</v>
+        <v>735</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>759</v>
+        <v>735</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -21785,26 +21838,32 @@
         <v>78</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>153</v>
+        <v>736</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O169" s="2"/>
-      <c r="P169" s="2"/>
+        <v>737</v>
+      </c>
+      <c r="O169" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="P169" t="s" s="2">
+        <v>739</v>
+      </c>
       <c r="Q169" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="R169" s="2"/>
+      <c r="R169" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="S169" t="s" s="2">
         <v>78</v>
       </c>
@@ -21848,7 +21907,7 @@
         <v>78</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>155</v>
+        <v>735</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>76</v>
@@ -21857,25 +21916,25 @@
         <v>84</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="F170" s="2"/>
       <c r="G170" t="s" s="2">
@@ -21891,21 +21950,23 @@
         <v>78</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>131</v>
+        <v>741</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>159</v>
+        <v>742</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="P170" s="2"/>
+        <v>743</v>
+      </c>
+      <c r="P170" t="s" s="2">
+        <v>744</v>
+      </c>
       <c r="Q170" t="s" s="2">
         <v>78</v>
       </c>
@@ -21929,13 +21990,13 @@
         <v>78</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>78</v>
+        <v>549</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>78</v>
+        <v>745</v>
       </c>
       <c r="AA170" t="s" s="2">
-        <v>78</v>
+        <v>746</v>
       </c>
       <c r="AB170" t="s" s="2">
         <v>78</v>
@@ -21953,7 +22014,7 @@
         <v>78</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>162</v>
+        <v>740</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>76</v>
@@ -21965,53 +22026,53 @@
         <v>78</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
-        <v>392</v>
+        <v>78</v>
       </c>
       <c r="F171" s="2"/>
       <c r="G171" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I171" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J171" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K171" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>393</v>
+        <v>748</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>394</v>
+        <v>749</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>133</v>
+        <v>750</v>
       </c>
       <c r="P171" t="s" s="2">
-        <v>139</v>
+        <v>751</v>
       </c>
       <c r="Q171" t="s" s="2">
         <v>78</v>
@@ -22060,30 +22121,30 @@
         <v>78</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>395</v>
+        <v>747</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>78</v>
+        <v>713</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -22106,17 +22167,19 @@
         <v>78</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="O172" s="2"/>
+        <v>754</v>
+      </c>
+      <c r="O172" t="s" s="2">
+        <v>755</v>
+      </c>
       <c r="P172" t="s" s="2">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="Q172" t="s" s="2">
         <v>78</v>
@@ -22165,7 +22228,7 @@
         <v>78</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>76</v>
@@ -22182,13 +22245,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -22196,7 +22259,7 @@
       </c>
       <c r="F173" s="2"/>
       <c r="G173" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>84</v>
@@ -22208,19 +22271,21 @@
         <v>78</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>174</v>
+        <v>505</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="O173" s="2"/>
-      <c r="P173" s="2"/>
+      <c r="P173" t="s" s="2">
+        <v>760</v>
+      </c>
       <c r="Q173" t="s" s="2">
         <v>78</v>
       </c>
@@ -22244,10 +22309,10 @@
         <v>78</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>549</v>
+        <v>78</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>769</v>
+        <v>78</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>78</v>
@@ -22268,10 +22333,10 @@
         <v>78</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI173" t="s" s="2">
         <v>84</v>
@@ -22285,13 +22350,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -22302,7 +22367,7 @@
         <v>76</v>
       </c>
       <c r="H174" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I174" t="s" s="2">
         <v>78</v>
@@ -22314,17 +22379,19 @@
         <v>78</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>203</v>
+        <v>762</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="O174" s="2"/>
+        <v>764</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>765</v>
+      </c>
       <c r="P174" t="s" s="2">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="Q174" t="s" s="2">
         <v>78</v>
@@ -22373,30 +22440,30 @@
         <v>78</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>96</v>
+        <v>767</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -22416,19 +22483,21 @@
         <v>78</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L175" t="s" s="2">
         <v>209</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="O175" s="2"/>
-      <c r="P175" s="2"/>
+      <c r="P175" t="s" s="2">
+        <v>771</v>
+      </c>
       <c r="Q175" t="s" s="2">
         <v>78</v>
       </c>
@@ -22476,7 +22545,7 @@
         <v>78</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>76</v>
@@ -22493,13 +22562,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>777</v>
+        <v>691</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -22513,7 +22582,7 @@
         <v>77</v>
       </c>
       <c r="I176" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J176" t="s" s="2">
         <v>78</v>
@@ -22522,16 +22591,18 @@
         <v>78</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>79</v>
+        <v>773</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="O176" s="2"/>
-      <c r="P176" s="2"/>
+      <c r="P176" t="s" s="2">
+        <v>776</v>
+      </c>
       <c r="Q176" t="s" s="2">
         <v>78</v>
       </c>
@@ -22579,7 +22650,7 @@
         <v>78</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>480</v>
+        <v>772</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>76</v>
@@ -22591,18 +22662,18 @@
         <v>78</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B177" t="s" s="2">
         <v>777</v>
       </c>
-      <c r="B177" t="s" s="2">
-        <v>782</v>
-      </c>
       <c r="C177" t="s" s="2">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -22610,10 +22681,10 @@
       </c>
       <c r="F177" s="2"/>
       <c r="G177" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I177" t="s" s="2">
         <v>78</v>
@@ -22625,13 +22696,13 @@
         <v>78</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>86</v>
+        <v>383</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>482</v>
+        <v>778</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" s="2"/>
@@ -22682,18 +22753,955 @@
         <v>78</v>
       </c>
       <c r="AG177" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="AH177" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI177" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK177" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="C178" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="D178" s="2"/>
+      <c r="E178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F178" s="2"/>
+      <c r="G178" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L178" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M178" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O178" s="2"/>
+      <c r="P178" s="2"/>
+      <c r="Q178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R178" s="2"/>
+      <c r="S178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF178" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG178" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AH178" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ178" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AK178" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="D179" s="2"/>
+      <c r="E179" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="F179" s="2"/>
+      <c r="G179" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H179" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L179" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M179" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O179" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="P179" s="2"/>
+      <c r="Q179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R179" s="2"/>
+      <c r="S179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG179" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AH179" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI179" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ179" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK179" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="AH177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ177" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK177" t="s" s="2">
+      <c r="C180" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="D180" s="2"/>
+      <c r="E180" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="F180" s="2"/>
+      <c r="G180" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H180" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J180" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K180" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L180" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M180" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O180" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="P180" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="Q180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R180" s="2"/>
+      <c r="S180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG180" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AH180" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI180" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK180" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="C181" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="D181" s="2"/>
+      <c r="E181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F181" s="2"/>
+      <c r="G181" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H181" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L181" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M181" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="N181" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="O181" s="2"/>
+      <c r="P181" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="Q181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R181" s="2"/>
+      <c r="S181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG181" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AH181" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI181" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ181" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK181" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="C182" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="D182" s="2"/>
+      <c r="E182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F182" s="2"/>
+      <c r="G182" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H182" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L182" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M182" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="O182" s="2"/>
+      <c r="P182" s="2"/>
+      <c r="Q182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R182" s="2"/>
+      <c r="S182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y182" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="Z182" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="AA182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG182" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="AH182" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI182" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK182" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="C183" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="D183" s="2"/>
+      <c r="E183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F183" s="2"/>
+      <c r="G183" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H183" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L183" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M183" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="O183" s="2"/>
+      <c r="P183" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="Q183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R183" s="2"/>
+      <c r="S183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG183" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="AH183" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI183" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK183" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="C184" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="D184" s="2"/>
+      <c r="E184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F184" s="2"/>
+      <c r="G184" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H184" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L184" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M184" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="O184" s="2"/>
+      <c r="P184" s="2"/>
+      <c r="Q184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R184" s="2"/>
+      <c r="S184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG184" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="AH184" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI184" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK184" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="C185" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="D185" s="2"/>
+      <c r="E185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F185" s="2"/>
+      <c r="G185" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L185" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M185" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="N185" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="O185" s="2"/>
+      <c r="P185" s="2"/>
+      <c r="Q185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R185" s="2"/>
+      <c r="S185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG185" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AH185" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK185" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="C186" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="D186" s="2"/>
+      <c r="E186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F186" s="2"/>
+      <c r="G186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L186" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M186" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="O186" s="2"/>
+      <c r="P186" s="2"/>
+      <c r="Q186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R186" s="2"/>
+      <c r="S186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG186" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="AH186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ186" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK186" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -1788,7 +1788,7 @@
     <t>Tillgängliggörande ändpunkt</t>
   </si>
   <si>
-    <t>2026-09-10T06:56:47+00:00</t>
+    <t>2026-09-10T07:38:29+00:00</t>
   </si>
   <si>
     <t>Den ändpunkt (TKEndpoint) som tillgängliggör denna API-instans ("tillgängliggör"). Basresursen CapabilityStatement har inget element för detta.</t>
